--- a/_qa/Entity_Tests.xlsx
+++ b/_qa/Entity_Tests.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
   <si>
     <t>Test ID</t>
   </si>
@@ -234,6 +234,907 @@
   </si>
   <si>
     <t>Editor navigates to or highlights the problematic entity</t>
+  </si>
+  <si>
+    <t>ENT-NAV-001</t>
+  </si>
+  <si>
+    <t>Navigate to Basic Settings tab</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram (entities represent things that flow through your simulation like customers, orders, or products)
+3. The right panel shows 'Entity Editor'</t>
+  </si>
+  <si>
+    <t>1. Look at the top of the Entity Editor panel - you'll see 2 small tab icons
+2. Find the gear icon (first tab) - this is the Basic Settings tab
+3. Click on the gear icon
+4. Observe what content appears in the panel below the tabs</t>
+  </si>
+  <si>
+    <t>1. The gear icon should appear highlighted or selected
+2. The panel below shows Basic Settings content:
+   - An 'Entity Name' text box near the top
+   - Possibly an info icon next to the name field
+3. The panel title may show 'Basic Settings' or similar</t>
+  </si>
+  <si>
+    <t>ENT-NAV-002</t>
+  </si>
+  <si>
+    <t>Navigate to States tab</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. The right panel shows 'Entity Editor'
+4. Currently on Basic Settings tab (gear icon selected)</t>
+  </si>
+  <si>
+    <t>1. Look at the tab icons at the top of the Entity Editor panel
+2. Find the second tab icon (to the right of the gear) - this is the States tab
+3. Click on the States tab icon
+4. Observe what content appears in the panel</t>
+  </si>
+  <si>
+    <t>1. The States tab icon should now appear highlighted or selected
+2. The panel below shows the States editor:
+   - A list of states (may be empty if none defined)
+   - An 'Add State' or '+' button to create new states
+3. NOTE: The Save/Cancel buttons disappear - States use auto-save</t>
+  </si>
+  <si>
+    <t>ENT-NAV-003</t>
+  </si>
+  <si>
+    <t>All tabs visible</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. The right panel shows 'Entity Editor'</t>
+  </si>
+  <si>
+    <t>1. Look at the top of the Entity Editor panel
+2. Count the number of tab icons visible
+3. Identify each tab by its icon:
+   - First tab: Gear icon (Basic Settings)
+   - Second tab: States icon
+4. Note the position and spacing of the tabs</t>
+  </si>
+  <si>
+    <t>1. Exactly 2 tab icons should be visible at the top of the panel
+2. Both icons should be clearly distinguishable
+3. The tabs should be evenly spaced and aligned
+4. One tab should appear selected/highlighted (usually Basic Settings by default)</t>
+  </si>
+  <si>
+    <t>ENT-NAV-004</t>
+  </si>
+  <si>
+    <t>Tab tooltips display</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. The right panel shows 'Entity Editor'
+4. Both tab icons are visible</t>
+  </si>
+  <si>
+    <t>1. Move your mouse cursor over the first tab icon (gear icon)
+2. Hold your mouse still for 1-2 seconds without clicking
+3. Observe if a tooltip appears
+4. Move your mouse away, then hover over the second tab icon
+5. Hold still for 1-2 seconds and observe</t>
+  </si>
+  <si>
+    <t>1. When hovering over the gear icon, a tooltip should appear saying 'Basic Settings' or similar
+2. When hovering over the States tab icon, a tooltip should appear saying 'States' or similar
+3. Tooltips should appear after a brief delay (1-2 seconds)
+4. Tooltips should disappear when you move the mouse away</t>
+  </si>
+  <si>
+    <t>ENT-BASIC-001</t>
+  </si>
+  <si>
+    <t>Edit entity name</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. The right panel shows 'Entity Editor'
+4. The Basic Settings tab (gear icon) is selected
+5. Note the current entity name displayed</t>
+  </si>
+  <si>
+    <t>1. Find the 'Entity Name' text box near the top of the panel
+2. Click inside the text box - you should see a blinking cursor
+3. Select all existing text (Ctrl+A or triple-click)
+4. Type a new name, for example: 'Customer Order'
+5. Press Tab or click somewhere outside the text box</t>
+  </si>
+  <si>
+    <t>1. The text box now displays your new name 'Customer Order'
+2. Look at the bottom of the panel
+3. The Save button (blue) should now be ENABLED (not grayed out)
+4. The Cancel button should also appear next to Save
+5. This indicates you have unsaved changes</t>
+  </si>
+  <si>
+    <t>ENT-BASIC-002</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Empty name handling</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. The right panel shows 'Entity Editor'
+4. The Basic Settings tab (gear icon) is selected</t>
+  </si>
+  <si>
+    <t>1. Find the 'Entity Name' text box near the top
+2. Click inside the text box
+3. Select all existing text (Ctrl+A)
+4. Press Delete or Backspace to clear all text
+5. The text box should now be completely empty
+6. Press Tab or click outside the text box</t>
+  </si>
+  <si>
+    <t>1. The text box accepts being empty (no crash)
+2. A placeholder text may appear like 'Enter entity name'
+3. The Save button should still become enabled
+4. If you try to save, validation may show an error about missing name
+5. The field should remain functional for typing a new name</t>
+  </si>
+  <si>
+    <t>ENT-BASIC-003</t>
+  </si>
+  <si>
+    <t>Special characters in name</t>
+  </si>
+  <si>
+    <t>1. Find the 'Entity Name' text box near the top
+2. Click inside and select all existing text
+3. Type a name with special characters: 'Test!@#$%Entity'
+4. Press Tab or click outside the text box
+5. Click Save to save the changes
+6. Click away from the entity, then click back on it</t>
+  </si>
+  <si>
+    <t>1. The text box should accept the special characters
+2. The name displays as 'Test!@#$%Entity'
+3. Save button enables and save completes successfully
+4. When re-selecting the entity, the name with special characters is preserved
+5. No error messages appear about invalid characters</t>
+  </si>
+  <si>
+    <t>ENT-BASIC-004</t>
+  </si>
+  <si>
+    <t>Very long name</t>
+  </si>
+  <si>
+    <t>1. Find the 'Entity Name' text box
+2. Click inside and select all existing text
+3. Type or paste a very long name (500+ characters)
+   Example: repeat 'VeryLongEntityName' many times
+4. Press Tab or click outside the text box
+5. Observe how the text box handles the long name</t>
+  </si>
+  <si>
+    <t>1. The text box should accept the long name without crashing
+2. The text may appear truncated in the display or show a scrollbar
+3. The Save button should become enabled
+4. The panel should remain responsive
+5. If saved and re-selected, the full name should be preserved</t>
+  </si>
+  <si>
+    <t>ENT-BASIC-005</t>
+  </si>
+  <si>
+    <t>Name info tooltip</t>
+  </si>
+  <si>
+    <t>1. Look next to the 'Entity Name' label or text box
+2. Find a small info icon (usually a circled 'i' or question mark)
+3. Move your mouse over the info icon
+4. Hold your mouse still for 1-2 seconds
+5. Read the tooltip that appears</t>
+  </si>
+  <si>
+    <t>1. An info icon should be visible near the Entity Name field
+2. Hovering shows a tooltip explaining what entities are
+3. The tooltip may explain that entities are 'templates' for things that flow through the simulation
+4. Example text: 'Entities define the types of items processed in your model'
+5. The tooltip disappears when you move the mouse away</t>
+  </si>
+  <si>
+    <t>ENT-BASIC-006</t>
+  </si>
+  <si>
+    <t>Placeholder text shown</t>
+  </si>
+  <si>
+    <t>1. Find the 'Entity Name' text box
+2. Click inside and select all existing text
+3. Press Delete or Backspace to clear the text completely
+4. Click outside the text box (don't type anything)
+5. Look at the empty text box</t>
+  </si>
+  <si>
+    <t>1. The empty text box should show placeholder text
+2. The placeholder appears in a lighter/grayed color
+3. Expected placeholder: 'Enter entity name' or similar
+4. The placeholder disappears when you click inside to type
+5. The placeholder reappears if you clear the field and click away</t>
+  </si>
+  <si>
+    <t>ENT-STATE-001</t>
+  </si>
+  <si>
+    <t>Add new state</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. The right panel shows 'Entity Editor'
+4. Click the States tab (second tab icon, to the right of the gear)</t>
+  </si>
+  <si>
+    <t>1. Look for an 'Add State' button or '+' icon in the States panel
+   - This is usually at the top or bottom of the states list
+2. Click the 'Add State' or '+' button
+3. Observe what happens in the states list below
+4. A new state should appear in the list</t>
+  </si>
+  <si>
+    <t>1. A new state is added to the list immediately
+2. The new state may have a default name like 'New State' or 'State 1'
+3. The state name field may be editable immediately (cursor in text box)
+4. IMPORTANT: Changes save automatically - no Save button needed
+5. The states list now shows one more item than before</t>
+  </si>
+  <si>
+    <t>ENT-STATE-002</t>
+  </si>
+  <si>
+    <t>Edit state name</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. The right panel shows 'Entity Editor'
+4. Click the States tab
+5. At least one state exists in the list</t>
+  </si>
+  <si>
+    <t>1. Find a state in the list (e.g., 'New State' or any existing state)
+2. Click on the state name to select it for editing
+   - Or click an edit icon/pencil if present
+3. The name should become editable (text box with cursor)
+4. Delete the existing name and type a new name: 'Active'
+5. Press Enter or click outside the text box</t>
+  </si>
+  <si>
+    <t>1. The state name changes to 'Active' immediately
+2. The change is saved automatically (no Save button to click)
+3. The state remains in the list with its new name
+4. No error messages appear
+5. If you click away and come back, the name 'Active' persists</t>
+  </si>
+  <si>
+    <t>ENT-STATE-003</t>
+  </si>
+  <si>
+    <t>Delete state</t>
+  </si>
+  <si>
+    <t>1. Find a state you want to delete in the list
+2. Look for a delete button next to the state:
+   - May be a trash can icon
+   - May be an 'X' button
+   - May appear when you hover over the state row
+3. Click the delete button for that state
+4. If a confirmation dialog appears, confirm the deletion</t>
+  </si>
+  <si>
+    <t>1. The state is removed from the list immediately
+2. The deletion is saved automatically (no Save button needed)
+3. The states list now shows one fewer item
+4. If you click away and come back, the deleted state is still gone
+5. No error messages appear during deletion</t>
+  </si>
+  <si>
+    <t>ENT-STATE-004</t>
+  </si>
+  <si>
+    <t>States auto-save</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. The right panel shows 'Entity Editor'
+4. Click the States tab</t>
+  </si>
+  <si>
+    <t>1. Add a new state by clicking the 'Add State' or '+' button
+2. Type a name for the state: 'Processing'
+3. Press Enter or click outside the text box
+4. DO NOT look for or click a Save button
+5. Immediately click on a different shape in the diagram
+6. Click back on the same Entity shape
+7. Go to the States tab again</t>
+  </si>
+  <si>
+    <t>1. When you return to the States tab, the 'Processing' state should still be there
+2. This proves that states save automatically without clicking Save
+3. There is no Save button visible on the States tab
+4. All changes (add, edit, delete) are saved immediately
+5. This is different from Basic Settings, which requires manual save</t>
+  </si>
+  <si>
+    <t>ENT-STATE-005</t>
+  </si>
+  <si>
+    <t>Save button hidden on States</t>
+  </si>
+  <si>
+    <t>1. Look at the bottom of the Entity Editor panel
+2. Look for any Save or Cancel buttons
+3. Compare to what you see when on the Basic Settings tab:
+   - Click the gear icon (Basic Settings tab)
+   - Make a change to the name
+   - Notice Save and Cancel buttons appear at the bottom
+4. Now click back to the States tab
+5. Look at the bottom of the panel again</t>
+  </si>
+  <si>
+    <t>1. On the States tab, there are NO Save or Cancel buttons at the bottom
+2. On the Basic Settings tab, Save/Cancel buttons ARE visible (when changes exist)
+3. This confirms States uses auto-save (no manual save needed)
+4. The footer area on States tab may be empty or show different content
+5. This is the expected behavior - not a bug</t>
+  </si>
+  <si>
+    <t>ENT-SAVE-001</t>
+  </si>
+  <si>
+    <t>Save button initially disabled</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. You have NOT made any changes to the entity yet</t>
+  </si>
+  <si>
+    <t>1. Click on any Entity shape in the diagram
+2. The right panel shows 'Entity Editor'
+3. Make sure you're on the Basic Settings tab (gear icon)
+4. Look at the bottom of the panel for the Save button
+5. Observe the state of the Save button WITHOUT making any changes</t>
+  </si>
+  <si>
+    <t>1. The Save button should be visible at the bottom right of the panel
+2. The Save button should be DISABLED (grayed out, not clickable)
+3. This is because no changes have been made yet
+4. The Cancel button may or may not be visible
+5. Hovering over the disabled Save button should show it's not clickable</t>
+  </si>
+  <si>
+    <t>ENT-SAVE-002</t>
+  </si>
+  <si>
+    <t>Save button enables on change</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. The right panel shows 'Entity Editor'
+4. The Basic Settings tab (gear icon) is selected
+5. The Save button is currently disabled (grayed out)</t>
+  </si>
+  <si>
+    <t>1. Find the 'Entity Name' text box near the top
+2. Click inside the text box
+3. Make any small change to the name:
+   - Add a letter at the end
+   - Or delete one character
+   - Or change any character
+4. Press Tab or click outside the text box
+5. Look at the Save button at the bottom</t>
+  </si>
+  <si>
+    <t>1. The Save button should now be ENABLED (blue, clickable)
+2. The button text should say 'Save' clearly
+3. The Cancel button should also appear next to it
+4. This indicates you have unsaved changes
+5. The button should respond to hover (cursor changes)</t>
+  </si>
+  <si>
+    <t>ENT-SAVE-003</t>
+  </si>
+  <si>
+    <t>Save persists changes</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. The right panel shows 'Entity Editor'
+4. Make a change to the entity name
+5. The Save button is now enabled (blue)</t>
+  </si>
+  <si>
+    <t>1. Note the new name you typed (e.g., 'Test Entity Save')
+2. Click the Save button at the bottom right
+3. Watch for any visual feedback (loading indicator, button change)
+4. After save completes, click on a different shape in the diagram
+5. Click back on the same Entity shape
+6. Check the entity name in the panel</t>
+  </si>
+  <si>
+    <t>1. When you click Save, the button may briefly show 'Saving...'
+2. After save, the Save button becomes disabled again (grayed out)
+3. The Cancel button may disappear
+4. When you re-select the entity, your saved name 'Test Entity Save' is displayed
+5. The change persisted successfully</t>
+  </si>
+  <si>
+    <t>ENT-SAVE-004</t>
+  </si>
+  <si>
+    <t>Cancel discards changes</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. Note the ORIGINAL entity name (e.g., 'Customer')
+4. The Basic Settings tab (gear icon) is selected</t>
+  </si>
+  <si>
+    <t>1. Find the 'Entity Name' text box
+2. Change the name to something different (e.g., 'SHOULD BE DISCARDED')
+3. The Save button is now enabled
+4. DO NOT click Save
+5. Instead, click the Cancel button (next to Save)
+6. Observe what happens to the entity name</t>
+  </si>
+  <si>
+    <t>1. When you click Cancel, the name reverts to the ORIGINAL value ('Customer')
+2. The text box now shows the original name, not 'SHOULD BE DISCARDED'
+3. The Save button becomes disabled again (no pending changes)
+4. The Cancel button may disappear
+5. Your changes were discarded without being saved</t>
+  </si>
+  <si>
+    <t>ENT-SAVE-005</t>
+  </si>
+  <si>
+    <t>Dirty state tracking</t>
+  </si>
+  <si>
+    <t>1. Change the entity name to something new (e.g., 'Pending Changes')
+2. The Save button should become enabled
+3. Now click on the States tab (second tab icon)
+4. Look around the States tab, don't make changes
+5. Click back to the Basic Settings tab (gear icon)
+6. Check the entity name and Save button state</t>
+  </si>
+  <si>
+    <t>1. When you return to Basic Settings, your change is still there
+2. The name still shows 'Pending Changes' (not lost)
+3. The Save button is still enabled (change still pending)
+4. Switching tabs does NOT discard your unsaved changes
+5. You can still click Save or Cancel after switching tabs</t>
+  </si>
+  <si>
+    <t>ENT-SAVE-006</t>
+  </si>
+  <si>
+    <t>Save shows loading state</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. The right panel shows 'Entity Editor'
+4. Make a change to enable the Save button</t>
+  </si>
+  <si>
+    <t>1. With the Save button enabled (blue), prepare to watch it closely
+2. Click the Save button
+3. Watch the button text and appearance during the save operation
+4. Note any changes in the button while saving</t>
+  </si>
+  <si>
+    <t>1. When clicked, the Save button should show a loading state:
+   - The text may change to 'Saving...' or show a spinner
+   - The button may become temporarily disabled during save
+2. After save completes (usually very quick):
+   - The button returns to normal 'Save' text
+   - The button becomes disabled (grayed out)
+3. This feedback confirms your save is being processed</t>
+  </si>
+  <si>
+    <t>ENT-SYNC-001</t>
+  </si>
+  <si>
+    <t>Switch to different entity</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has at least 2 Entity shapes in the diagram
+3. Click on the first Entity shape
+4. Note the name shown in the Entity Editor panel</t>
+  </si>
+  <si>
+    <t>1. With the first Entity selected, note its name (e.g., 'Customer')
+2. Now click on a DIFFERENT Entity shape in the diagram
+3. Observe the Entity Editor panel on the right
+4. Look at the entity name displayed in the Basic Settings tab</t>
+  </si>
+  <si>
+    <t>1. The panel should update to show the NEW entity's data
+2. The entity name should change to the second entity's name
+3. The panel title may still say 'Entity Editor'
+4. The transition should be smooth with no errors
+5. All fields should reflect the newly selected entity's values</t>
+  </si>
+  <si>
+    <t>ENT-SYNC-002</t>
+  </si>
+  <si>
+    <t>Switch with unsaved changes</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has at least 2 Entity shapes in the diagram
+3. Click on the first Entity shape
+4. The Basic Settings tab is showing</t>
+  </si>
+  <si>
+    <t>1. Change the entity name to 'UNSAVED CHANGE'
+2. The Save button should become enabled (blue)
+3. DO NOT click Save - leave the change unsaved
+4. Now click on a DIFFERENT Entity shape in the diagram
+5. Observe what happens to the panel and the first entity's changes</t>
+  </si>
+  <si>
+    <t>1. When you click a different entity, the panel loads the NEW entity's data
+2. The unsaved changes to the first entity are DISCARDED (lost)
+3. There may or may not be a warning about unsaved changes
+4. The new entity's name appears in the panel (not 'UNSAVED CHANGE')
+5. This is expected behavior - switching entities abandons unsaved changes</t>
+  </si>
+  <si>
+    <t>ENT-SYNC-003</t>
+  </si>
+  <si>
+    <t>External update sync</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Be in a collaborative editing session (multiple users editing same document)
+3. Click on an Entity shape
+4. The Entity Editor shows the current entity data</t>
+  </si>
+  <si>
+    <t>1. Have another user (or another browser window) edit the SAME entity
+2. The other user changes the entity name and saves
+3. Observe your Entity Editor panel:
+   - Does it automatically update?
+   - Or do you need to click away and back?
+4. Note any sync behavior or notifications</t>
+  </si>
+  <si>
+    <t>1. The panel should eventually reflect the changes made by the other user
+2. This may happen automatically, or may require re-selecting the entity
+3. The updated name from the other user should appear
+4. There should be no data conflicts or errors
+5. Note: Real-time sync behavior may vary - document observed behavior</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model currently has entity shapes that can be deleted
+3. You have access to the Model Panel (main Quodsi panel)</t>
+  </si>
+  <si>
+    <t>1. Delete ALL entity shapes from your model:
+   - Select each Entity shape and press Delete
+   - Or right-click and choose Delete
+   - Continue until no Entity shapes remain
+2. Open the Model Panel if not already open
+3. Look for a Validation tab or section
+4. Click on the Validation tab/section to view validation messages</t>
+  </si>
+  <si>
+    <t>1. The Validation section should show an ERROR message
+2. The error should indicate something like:
+   - 'No entities defined'
+   - 'Model requires at least one entity'
+   - Or similar message about missing entities
+3. The error should be marked as ERROR (not just warning)
+4. This error blocks simulation runs</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has at least one Entity shape
+3. Click on an Entity to open the Entity Editor</t>
+  </si>
+  <si>
+    <t>1. Go to the Basic Settings tab (gear icon)
+2. Find the 'Entity Name' text box
+3. Clear the name completely (select all, delete)
+4. Click Save to save the empty name
+5. Open the Model Panel's Validation tab
+6. Look for validation messages related to this entity</t>
+  </si>
+  <si>
+    <t>1. The Validation section should show an ERROR for this entity
+2. The error should indicate:
+   - 'Missing name' or 'Name is required'
+   - Or 'Entity has no name'
+3. The error should identify which entity has the problem
+4. This is an ERROR level issue (not just warning)
+5. Clicking the error may navigate to or highlight the entity</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has at least one Entity with a default/generic name</t>
+  </si>
+  <si>
+    <t>1. Create a new Entity shape or find one with the default name 'New Entity'
+2. Do NOT change the name from the default
+3. Save any pending changes
+4. Open the Model Panel's Validation tab
+5. Look for warnings related to entity names</t>
+  </si>
+  <si>
+    <t>1. The Validation section should show a WARNING (not error)
+2. The warning should indicate something like:
+   - 'Entity is using default name'
+   - 'Consider renaming entity from New Entity'
+3. The warning identifies the entity with the default name
+4. This is a WARNING level (yellow) not ERROR (red)
+5. The simulation can still run with this warning</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Create or have an Entity shape in the diagram
+3. Do NOT assign this entity to any Generator</t>
+  </si>
+  <si>
+    <t>1. Create a new Entity shape if needed
+2. Give it a name like 'Unused Entity'
+3. Make sure no Generator is using this entity:
+   - Check all Generators' settings
+   - None should reference 'Unused Entity'
+4. Open the Model Panel's Validation tab
+5. Look for warnings about unused entities</t>
+  </si>
+  <si>
+    <t>1. The Validation section should show a WARNING
+2. The warning should indicate:
+   - 'Entity not used by any generator'
+   - Or 'Entity is not referenced in the model'
+3. The warning identifies 'Unused Entity' specifically
+4. This is a WARNING level - simulation can run but entity serves no purpose
+5. To fix: assign this entity to a Generator's entity type setting</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has at least 2 Entity shapes</t>
+  </si>
+  <si>
+    <t>1. Click on the first Entity shape
+2. Set its name to 'CustomerOrder' and Save
+3. Click on the second Entity shape
+4. Set its name to EXACTLY the same: 'CustomerOrder' and Save
+5. Open the Model Panel's Validation tab
+6. Look for warnings about duplicate names</t>
+  </si>
+  <si>
+    <t>1. The Validation section should show a WARNING about duplicate names
+2. The warning should indicate:
+   - 'Entity has name conflict with other entities'
+   - Or 'Duplicate entity name: CustomerOrder'
+3. The warning may list both entities with the same name
+4. This is a WARNING level (simulation may still run)
+5. Recommended to fix by giving each entity a unique name</t>
+  </si>
+  <si>
+    <t>1. Click on the first Entity shape
+2. Set its name to 'Customer' (capital C) and Save
+3. Click on the second Entity shape
+4. Set its name to 'customer' (lowercase c) and Save
+5. Open the Model Panel's Validation tab
+6. Look for any duplicate name warnings</t>
+  </si>
+  <si>
+    <t>1. Check if the validation detects this as a duplicate:
+   - Some systems consider 'Customer' and 'customer' the same
+   - Others treat them as different names
+2. If detected: Warning about name conflict should appear
+3. If not detected: No warning appears
+4. Document the actual behavior you observe
+5. Note: Case-sensitivity rules vary by system</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has a 'default' entity (if the system has this concept)
+3. Or note: this test may not apply if there's no default entity concept</t>
+  </si>
+  <si>
+    <t>1. Identify if your model has a 'default' entity type
+   - This might be an entity marked as default
+   - Or an entity with a special designation
+2. Make sure this default entity is NOT assigned to any Generator
+3. Open the Model Panel's Validation tab
+4. Check for 'entity not used' warnings
+5. Note whether the default entity triggers this warning</t>
+  </si>
+  <si>
+    <t>1. If a 'default' entity exists:
+   - It should NOT show 'not used' warning even if unassigned
+   - Default entities may be implicitly used by the system
+2. If no default entity concept exists:
+   - All unused entities should show warnings
+3. Document the actual behavior observed
+4. Note: This test verifies special handling for default entities</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Have an Entity with a validation error (e.g., empty name)
+3. The error is visible in the Validation tab</t>
+  </si>
+  <si>
+    <t>1. Note the current validation error (e.g., 'Missing name')
+2. Click on the Entity with the error
+3. Fix the issue:
+   - If empty name: type a valid name and Save
+4. After saving, return to the Model Panel's Validation tab
+5. Look for the error you just fixed</t>
+  </si>
+  <si>
+    <t>1. The error that was previously shown should now be GONE
+2. The validation list should no longer include that error
+3. If this was the only error, the validation section may show 'No errors'
+4. The fix was successful
+5. Note: May need to refresh or re-check validation to see update</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Create an Entity with multiple issues:
+   - Empty or missing name
+   - Not used by any generator
+   - Or other issues</t>
+  </si>
+  <si>
+    <t>1. Create or modify an Entity to have multiple problems:
+   - Clear the name (empty name error)
+   - Make sure it's not used by any Generator (unused warning)
+2. Save the entity
+3. Open the Model Panel's Validation tab
+4. Look at all the validation messages for this entity</t>
+  </si>
+  <si>
+    <t>1. Multiple validation issues should be listed SEPARATELY
+2. You should see distinct messages like:
+   - ERROR: 'Missing name' or similar
+   - WARNING: 'Entity not used' or similar
+3. Each issue should be its own line item
+4. Issues are NOT combined into one message
+5. You can address each issue independently</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Have an Entity with a validation error visible in the Validation tab
+3. The Entity Editor is not currently showing that entity</t>
+  </si>
+  <si>
+    <t>1. Open the Model Panel's Validation tab
+2. Find a validation error related to an Entity
+3. Click directly on the error message or error item
+4. Observe what happens in the main diagram and panels</t>
+  </si>
+  <si>
+    <t>1. Clicking the error should navigate to or highlight the Entity:
+   - The diagram may zoom/pan to show the Entity
+   - The Entity may become selected (highlighted)
+   - The Entity Editor may open for that Entity
+2. This helps you quickly find and fix the problem
+3. You should now be able to edit the Entity directly
+4. If navigation doesn't work, document actual behavior</t>
+  </si>
+  <si>
+    <t>ENT-EDGE-001</t>
+  </si>
+  <si>
+    <t>Invalid entity data</t>
+  </si>
+  <si>
+    <t>1. This test requires technical setup or a corrupted entity
+2. Normal users cannot easily reproduce this scenario
+3. This tests error handling for programmatic issues</t>
+  </si>
+  <si>
+    <t>1. If possible, create a scenario where an entity has missing or corrupted data:
+   - An entity with a missing internal ID
+   - Or entity data that was corrupted somehow
+2. Try to open/select this corrupted entity in LucidChart
+3. Observe the Entity Editor panel
+4. Note any error messages displayed</t>
+  </si>
+  <si>
+    <t>1. The system should handle the error gracefully
+2. An error message should appear like:
+   - 'Invalid entity data'
+   - 'Unable to load entity'
+   - Or similar error indication
+3. The application should NOT crash
+4. Other entities should still be accessible
+5. Note: This is a defensive error handling test</t>
+  </si>
+  <si>
+    <t>ENT-EDGE-002</t>
+  </si>
+  <si>
+    <t>Browser refresh during edit</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Entity shape in the diagram
+3. The Entity Editor panel is open
+4. Note the current entity name for reference</t>
+  </si>
+  <si>
+    <t>1. Make a change to the entity name:
+   - Type a new name like 'UNSAVED REFRESH TEST'
+2. DO NOT click Save - leave the change unsaved
+3. The Save button should be enabled (blue)
+4. Press F5 or Ctrl+R to refresh the browser
+5. Wait for LucidChart to fully reload
+6. Click on the same Entity shape again
+7. Check the entity name</t>
+  </si>
+  <si>
+    <t>1. When you refresh, you may see a browser warning about unsaved changes
+2. After refresh, the page reloads completely
+3. When you re-select the entity, it shows the ORIGINAL name
+4. The unsaved change 'UNSAVED REFRESH TEST' is LOST
+5. This is expected behavior - browser refresh loses unsaved work
+6. No errors or crashes should occur</t>
+  </si>
+  <si>
+    <t>ENT-EDGE-003</t>
+  </si>
+  <si>
+    <t>Default name fallback</t>
+  </si>
+  <si>
+    <t>1. This tests the system's handling of missing name data
+2. May require technical setup to create entity without name
+3. Or may occur if data becomes corrupted</t>
+  </si>
+  <si>
+    <t>1. If possible, create or find an entity where:
+   - The name field is null (no value)
+   - Or the name field is undefined
+   - This might happen with corrupted data
+2. Try to select/load this entity
+3. Look at the Entity Name field in the Basic Settings tab
+4. Note what value appears in the name field</t>
+  </si>
+  <si>
+    <t>1. Instead of showing null/undefined/error, the system should show a default:
+   - 'New Entity' or similar default name
+   - Or an empty field with placeholder text
+2. The panel should NOT crash or show 'undefined'
+3. The entity should be editable
+4. You should be able to type a proper name and save
+5. This tests graceful handling of missing data</t>
   </si>
 </sst>
 </file>
@@ -280,9 +1181,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
   </cellXfs>
@@ -645,285 +1549,305 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ENT-STATE-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Add new state</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>States tab open</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Click add state in States editor</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>New state added to list</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="A2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ENT-STATE-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Edit state name</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>State exists</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Change state name</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>State name updates</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="A3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ENT-STATE-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Delete state</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>State exists</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Remove a state</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>State removed from list</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="A4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ENT-STATE-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>States auto-save</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>States tab open</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Make change to state</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Saves immediately (no Save button)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ENT-STATE-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Save button hidden on States</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>States tab open</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Observe footer area</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Save/Cancel buttons not shown</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="A6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -931,205 +1855,217 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ENT-SYNC-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Switch to different entity</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Multiple entities exist</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Select different entity in panel</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Form loads new entity data</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="A2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ENT-SYNC-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Switch with unsaved changes</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Changes made, not saved</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Make changes, select different entity</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Changes auto-discarded, new entity loads</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="A3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ENT-SYNC-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>External update sync</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Collaborative editing</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Another user updates same entity</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Form reflects latest data</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="A4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1137,245 +2073,261 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ENT-NAV-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Navigate to Basic tab</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Entity selected</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Click Basic Settings icon</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Basic Settings content displays</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ENT-NAV-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Navigate to States tab</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Entity selected</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Click States icon</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>States editor displays</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ENT-NAV-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>All tabs visible</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Entity selected</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Observe tab bar</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Both tab icons visible (Basic, States)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="A4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ENT-NAV-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tab tooltips display</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Entity selected</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Hover over each tab icon</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tooltip shows tab description</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1383,205 +2335,217 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ENT-EDGE-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Invalid entity data</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Corrupt entity</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Open editor with missing ID</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Error message 'Invalid entity data' shown</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="A2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ENT-EDGE-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Browser refresh during edit</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Changes made, not saved</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Make changes, refresh browser</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Changes are lost (expected)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="A3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ENT-EDGE-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Default name fallback</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Entity with no name</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Load entity with null/undefined name</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Name defaults to 'New Entity'</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="A4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1589,325 +2553,349 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ENT-BASIC-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Edit entity name</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Basic tab open</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Type new name in Name field</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Name updates, Save button enables</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="A2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ENT-BASIC-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Empty name handling</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Basic tab open</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Clear name field completely</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Field accepts empty</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ENT-BASIC-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Special characters in name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Basic tab open</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Enter name with special chars (!@#$%)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Accepts special characters</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ENT-BASIC-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Very long name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Basic tab open</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Enter 500+ character name</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Handles gracefully</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ENT-BASIC-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Name info tooltip</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Basic tab open</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Hover over name info icon</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tooltip explains entity template concept</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="A6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ENT-BASIC-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Placeholder text shown</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Basic tab open, name empty</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Clear name field</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Placeholder 'Enter entity name' shown</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="A7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1915,325 +2903,349 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ENT-SAVE-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Save button initially disabled</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Entity just selected</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Open entity with no changes</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Save button is disabled/grayed</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="A2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ENT-SAVE-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Save button enables on change</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Entity selected</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Make any change to name field</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Save button becomes enabled</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ENT-SAVE-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Save persists changes</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Changes made</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Make change, click Save</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Changes saved, Save button disables</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="A4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ENT-SAVE-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Cancel discards changes</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Changes made</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Make changes, click Cancel</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Form resets to original values</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="A5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ENT-SAVE-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Dirty state tracking</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Changes made</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Make change, switch to States tab, return</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Changes still present</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="A6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ENT-SAVE-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Save shows loading state</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Changes made</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Click Save button</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Button shows 'Saving...' text</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="A7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2245,46 +3257,46 @@
   <dimension ref="A1:N11"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2299,13 +3311,13 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>180</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>182</v>
       </c>
       <c r="G2" t="s">
         <v>20</v>
@@ -2343,13 +3355,13 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>184</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
@@ -2387,13 +3399,13 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>186</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>187</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
@@ -2431,13 +3443,13 @@
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>190</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>191</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
@@ -2475,13 +3487,13 @@
         <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>193</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>194</v>
       </c>
       <c r="G6" t="s">
         <v>20</v>
@@ -2519,13 +3531,13 @@
         <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>195</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="G7" t="s">
         <v>20</v>
@@ -2563,13 +3575,13 @@
         <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>197</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>198</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>199</v>
       </c>
       <c r="G8" t="s">
         <v>20</v>
@@ -2607,13 +3619,13 @@
         <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>200</v>
       </c>
       <c r="E9" t="s">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>202</v>
       </c>
       <c r="G9" t="s">
         <v>20</v>
@@ -2651,13 +3663,13 @@
         <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>203</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>204</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>205</v>
       </c>
       <c r="G10" t="s">
         <v>20</v>
@@ -2695,13 +3707,13 @@
         <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>206</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>207</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>208</v>
       </c>
       <c r="G11" t="s">
         <v>20</v>
